--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/35.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/35.xlsx
@@ -426,13 +426,13 @@
         <v>-24.9272770765424</v>
       </c>
       <c r="E2">
-        <v>-6.503453996919363</v>
+        <v>-4.239094110143568</v>
       </c>
       <c r="F2">
-        <v>2.896932370759409</v>
+        <v>2.830797174054702</v>
       </c>
       <c r="G2">
-        <v>-18.54281683032992</v>
+        <v>-15.71200082928103</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-24.82927854587784</v>
       </c>
       <c r="E3">
-        <v>-6.665844559720158</v>
+        <v>-5.157846753365513</v>
       </c>
       <c r="F3">
-        <v>2.928310927977454</v>
+        <v>2.93206177557733</v>
       </c>
       <c r="G3">
-        <v>-17.05680320039726</v>
+        <v>-14.55085911866044</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-24.32862156474762</v>
       </c>
       <c r="E4">
-        <v>-9.321254211996509</v>
+        <v>-5.376700224127354</v>
       </c>
       <c r="F4">
-        <v>2.994697948372612</v>
+        <v>2.436177853974268</v>
       </c>
       <c r="G4">
-        <v>-17.54318230697707</v>
+        <v>-14.43483893440366</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-23.41373569225807</v>
       </c>
       <c r="E5">
-        <v>-9.202140111200427</v>
+        <v>-6.18111495957677</v>
       </c>
       <c r="F5">
-        <v>3.375708848759856</v>
+        <v>2.994974623085147</v>
       </c>
       <c r="G5">
-        <v>-16.1412542334627</v>
+        <v>-14.58920573521471</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-22.1042165240689</v>
       </c>
       <c r="E6">
-        <v>-10.16002431152491</v>
+        <v>-6.747820644849624</v>
       </c>
       <c r="F6">
-        <v>3.425556685590719</v>
+        <v>3.106618668164853</v>
       </c>
       <c r="G6">
-        <v>-14.92739245194146</v>
+        <v>-13.08325384883972</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.47086837034018</v>
       </c>
       <c r="E7">
-        <v>-10.84240939182821</v>
+        <v>-8.314362118039051</v>
       </c>
       <c r="F7">
-        <v>3.055674072892683</v>
+        <v>3.054537552816043</v>
       </c>
       <c r="G7">
-        <v>-15.61659247357109</v>
+        <v>-12.57403986469374</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.57792511431876</v>
       </c>
       <c r="E8">
-        <v>-12.41006392565269</v>
+        <v>-9.137188039291432</v>
       </c>
       <c r="F8">
-        <v>3.184022975017244</v>
+        <v>3.205091671540047</v>
       </c>
       <c r="G8">
-        <v>-15.01260454465081</v>
+        <v>-12.11353193163956</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.50809130953955</v>
       </c>
       <c r="E9">
-        <v>-11.37449806070862</v>
+        <v>-9.052105352090996</v>
       </c>
       <c r="F9">
-        <v>3.625526233361325</v>
+        <v>3.51564329737997</v>
       </c>
       <c r="G9">
-        <v>-13.24480150264863</v>
+        <v>-11.54368601510956</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.34883672426761</v>
       </c>
       <c r="E10">
-        <v>-11.94221712954473</v>
+        <v>-9.467775354325136</v>
       </c>
       <c r="F10">
-        <v>3.473487680251504</v>
+        <v>3.467748750884909</v>
       </c>
       <c r="G10">
-        <v>-12.76440622267165</v>
+        <v>-10.81986229871258</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.17136896256289</v>
       </c>
       <c r="E11">
-        <v>-13.00528140667049</v>
+        <v>-11.28681961643017</v>
       </c>
       <c r="F11">
-        <v>3.339784211235246</v>
+        <v>3.526349117693751</v>
       </c>
       <c r="G11">
-        <v>-11.97726933919559</v>
+        <v>-9.907784316711906</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.06776073670759</v>
       </c>
       <c r="E12">
-        <v>-13.55386663093312</v>
+        <v>-11.10239211433983</v>
       </c>
       <c r="F12">
-        <v>4.214077959580762</v>
+        <v>3.657930309424036</v>
       </c>
       <c r="G12">
-        <v>-11.73450925339092</v>
+        <v>-8.937101645502214</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.093720534413245</v>
       </c>
       <c r="E13">
-        <v>-14.69865364729754</v>
+        <v>-11.56551255596013</v>
       </c>
       <c r="F13">
-        <v>4.249558592177471</v>
+        <v>3.75979133547668</v>
       </c>
       <c r="G13">
-        <v>-10.51648855573604</v>
+        <v>-8.654423274899422</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.329467219710603</v>
       </c>
       <c r="E14">
-        <v>-16.10049537218956</v>
+        <v>-13.17873197122931</v>
       </c>
       <c r="F14">
-        <v>4.453998010453583</v>
+        <v>3.693230357926934</v>
       </c>
       <c r="G14">
-        <v>-10.11794795092423</v>
+        <v>-7.426261139880364</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.819041361136645</v>
       </c>
       <c r="E15">
-        <v>-17.23056756083011</v>
+        <v>-13.24796185080288</v>
       </c>
       <c r="F15">
-        <v>4.722758500822271</v>
+        <v>3.802054640367511</v>
       </c>
       <c r="G15">
-        <v>-9.606929942265785</v>
+        <v>-6.383905697410837</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.593273115746099</v>
       </c>
       <c r="E16">
-        <v>-18.27216804182916</v>
+        <v>-14.18020412440787</v>
       </c>
       <c r="F16">
-        <v>5.183262850651767</v>
+        <v>4.070304856416074</v>
       </c>
       <c r="G16">
-        <v>-9.112808672601023</v>
+        <v>-5.767474959769306</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.661994783873345</v>
       </c>
       <c r="E17">
-        <v>-16.24739445674875</v>
+        <v>-15.72140270209319</v>
       </c>
       <c r="F17">
-        <v>4.862649874337441</v>
+        <v>4.095967678554803</v>
       </c>
       <c r="G17">
-        <v>-8.163350049544785</v>
+        <v>-5.123696672535863</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.998534157490725</v>
       </c>
       <c r="E18">
-        <v>-20.32605148508529</v>
+        <v>-16.44749617837899</v>
       </c>
       <c r="F18">
-        <v>5.3965260385025</v>
+        <v>4.332975189639381</v>
       </c>
       <c r="G18">
-        <v>-7.917334365234999</v>
+        <v>-4.46310257939106</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.578065379684508</v>
       </c>
       <c r="E19">
-        <v>-19.82756644903407</v>
+        <v>-16.99632228889846</v>
       </c>
       <c r="F19">
-        <v>5.14314004712977</v>
+        <v>4.402637574745208</v>
       </c>
       <c r="G19">
-        <v>-6.981570402931446</v>
+        <v>-3.543412971534991</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.34579336532029</v>
       </c>
       <c r="E20">
-        <v>-19.19103282175688</v>
+        <v>-17.38936144262361</v>
       </c>
       <c r="F20">
-        <v>5.973220513718266</v>
+        <v>4.799793355813015</v>
       </c>
       <c r="G20">
-        <v>-6.974080176699542</v>
+        <v>-3.096333403285206</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.263233242415303</v>
       </c>
       <c r="E21">
-        <v>-20.22642840503663</v>
+        <v>-18.23702772080979</v>
       </c>
       <c r="F21">
-        <v>4.930637300554808</v>
+        <v>4.63438826629162</v>
       </c>
       <c r="G21">
-        <v>-6.414735980287294</v>
+        <v>-2.834885607697348</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.285632394695227</v>
       </c>
       <c r="E22">
-        <v>-20.06388002020549</v>
+        <v>-18.18356343142527</v>
       </c>
       <c r="F22">
-        <v>5.799892918356496</v>
+        <v>4.705738864164353</v>
       </c>
       <c r="G22">
-        <v>-6.105524612405019</v>
+        <v>-2.477693975719593</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.377314719147686</v>
       </c>
       <c r="E23">
-        <v>-21.76116873911185</v>
+        <v>-17.88492677111347</v>
       </c>
       <c r="F23">
-        <v>6.419945800169594</v>
+        <v>4.917136568623981</v>
       </c>
       <c r="G23">
-        <v>-6.705139544135189</v>
+        <v>-2.21250498313267</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.513863444837052</v>
       </c>
       <c r="E24">
-        <v>-21.79871792269962</v>
+        <v>-19.09219469864861</v>
       </c>
       <c r="F24">
-        <v>5.659212939073862</v>
+        <v>4.797473927085176</v>
       </c>
       <c r="G24">
-        <v>-5.914692236517593</v>
+        <v>-2.514823985294405</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.673189888750035</v>
       </c>
       <c r="E25">
-        <v>-21.77288910147051</v>
+        <v>-18.8330675376699</v>
       </c>
       <c r="F25">
-        <v>6.113438263990138</v>
+        <v>4.568065858553881</v>
       </c>
       <c r="G25">
-        <v>-6.015973462185242</v>
+        <v>-2.654021054658793</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.843668474243024</v>
       </c>
       <c r="E26">
-        <v>-20.9478162928914</v>
+        <v>-19.81555120867134</v>
       </c>
       <c r="F26">
-        <v>6.171543267092106</v>
+        <v>4.555678452412417</v>
       </c>
       <c r="G26">
-        <v>-6.763267772456326</v>
+        <v>-2.642901893445241</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.015669479292635</v>
       </c>
       <c r="E27">
-        <v>-19.54079136026599</v>
+        <v>-18.59116789726659</v>
       </c>
       <c r="F27">
-        <v>6.011194532197401</v>
+        <v>4.511715337611042</v>
       </c>
       <c r="G27">
-        <v>-7.170434277397172</v>
+        <v>-2.269004106828952</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.183337763305532</v>
       </c>
       <c r="E28">
-        <v>-19.66058658771934</v>
+        <v>-19.14560084307458</v>
       </c>
       <c r="F28">
-        <v>5.673724279236104</v>
+        <v>4.895357132869576</v>
       </c>
       <c r="G28">
-        <v>-6.299270579256127</v>
+        <v>-2.597997086478093</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.344498112009669</v>
       </c>
       <c r="E29">
-        <v>-21.42033129852847</v>
+        <v>-19.28847131264868</v>
       </c>
       <c r="F29">
-        <v>5.994893918445111</v>
+        <v>4.505017158792005</v>
       </c>
       <c r="G29">
-        <v>-7.454710423689725</v>
+        <v>-3.425070529964417</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.496911756844706</v>
       </c>
       <c r="E30">
-        <v>-20.27517879956747</v>
+        <v>-19.37062598586511</v>
       </c>
       <c r="F30">
-        <v>5.868127198059898</v>
+        <v>4.390294900443496</v>
       </c>
       <c r="G30">
-        <v>-6.794539271168682</v>
+        <v>-2.934182667475751</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.642040128564244</v>
       </c>
       <c r="E31">
-        <v>-19.96415726308503</v>
+        <v>-19.74713120530612</v>
       </c>
       <c r="F31">
-        <v>6.097522012712748</v>
+        <v>4.733674726456363</v>
       </c>
       <c r="G31">
-        <v>-6.426142323405868</v>
+        <v>-3.24157434637802</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.782423446768241</v>
       </c>
       <c r="E32">
-        <v>-21.01714584953676</v>
+        <v>-18.94349312037445</v>
       </c>
       <c r="F32">
-        <v>5.815896976578583</v>
+        <v>4.535882128220314</v>
       </c>
       <c r="G32">
-        <v>-6.090698193872086</v>
+        <v>-3.016097389766521</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.919589874108016</v>
       </c>
       <c r="E33">
-        <v>-20.77257154104026</v>
+        <v>-19.02036075557437</v>
       </c>
       <c r="F33">
-        <v>5.80862888098642</v>
+        <v>4.799627682332455</v>
       </c>
       <c r="G33">
-        <v>-7.260771261738874</v>
+        <v>-3.239216844012244</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.058142828112488</v>
       </c>
       <c r="E34">
-        <v>-20.20146345176309</v>
+        <v>-18.48055126684111</v>
       </c>
       <c r="F34">
-        <v>6.624524384169376</v>
+        <v>5.099026169461085</v>
       </c>
       <c r="G34">
-        <v>-6.694861042679976</v>
+        <v>-3.437053847637627</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.199000494707555</v>
       </c>
       <c r="E35">
-        <v>-19.04851122193406</v>
+        <v>-17.6983852844588</v>
       </c>
       <c r="F35">
-        <v>6.326615301630979</v>
+        <v>5.410303445145861</v>
       </c>
       <c r="G35">
-        <v>-7.135625219763859</v>
+        <v>-3.964079636756484</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.344699828762348</v>
       </c>
       <c r="E36">
-        <v>-19.41783553899444</v>
+        <v>-17.01045566703685</v>
       </c>
       <c r="F36">
-        <v>6.456271367517158</v>
+        <v>5.184344698479824</v>
       </c>
       <c r="G36">
-        <v>-7.975016156231056</v>
+        <v>-3.64502315102112</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.494022499835798</v>
       </c>
       <c r="E37">
-        <v>-18.42641415722197</v>
+        <v>-17.20421128176275</v>
       </c>
       <c r="F37">
-        <v>6.206589835169748</v>
+        <v>5.599707995061163</v>
       </c>
       <c r="G37">
-        <v>-7.198293532928942</v>
+        <v>-4.101506621288096</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.646011085204496</v>
       </c>
       <c r="E38">
-        <v>-19.03134184631722</v>
+        <v>-17.19984210344903</v>
       </c>
       <c r="F38">
-        <v>6.199064945682717</v>
+        <v>5.632942095261479</v>
       </c>
       <c r="G38">
-        <v>-7.230987887443454</v>
+        <v>-3.942564490581119</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.797557079767042</v>
       </c>
       <c r="E39">
-        <v>-18.73521372564562</v>
+        <v>-16.56251521280879</v>
       </c>
       <c r="F39">
-        <v>7.013303714060074</v>
+        <v>5.819720720509905</v>
       </c>
       <c r="G39">
-        <v>-6.946962372631648</v>
+        <v>-3.874933151948329</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.942697410924434</v>
       </c>
       <c r="E40">
-        <v>-17.05258999592724</v>
+        <v>-16.38272269455696</v>
       </c>
       <c r="F40">
-        <v>6.627986959913079</v>
+        <v>6.289178065228858</v>
       </c>
       <c r="G40">
-        <v>-7.815511410064694</v>
+        <v>-4.010890287275145</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.077124679277351</v>
       </c>
       <c r="E41">
-        <v>-18.72170332920595</v>
+        <v>-15.36240326838634</v>
       </c>
       <c r="F41">
-        <v>7.067203924225432</v>
+        <v>6.201475494824863</v>
       </c>
       <c r="G41">
-        <v>-8.248209691734333</v>
+        <v>-4.774167575933025</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.192298176058528</v>
       </c>
       <c r="E42">
-        <v>-17.00977454037958</v>
+        <v>-15.69687383600875</v>
       </c>
       <c r="F42">
-        <v>6.924529236236856</v>
+        <v>6.393307161230368</v>
       </c>
       <c r="G42">
-        <v>-8.040693352537398</v>
+        <v>-4.732604522042502</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.283562881685731</v>
       </c>
       <c r="E43">
-        <v>-16.98463099901906</v>
+        <v>-14.1231016219028</v>
       </c>
       <c r="F43">
-        <v>6.653732618792088</v>
+        <v>6.331999689749176</v>
       </c>
       <c r="G43">
-        <v>-8.207818862165219</v>
+        <v>-5.374576174018895</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.345060188661533</v>
       </c>
       <c r="E44">
-        <v>-16.00174861973044</v>
+        <v>-14.20031397364269</v>
       </c>
       <c r="F44">
-        <v>6.453174930165494</v>
+        <v>6.017412257922813</v>
       </c>
       <c r="G44">
-        <v>-8.428877133556258</v>
+        <v>-5.462077889734648</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.377117983523303</v>
       </c>
       <c r="E45">
-        <v>-13.64166136512867</v>
+        <v>-13.56062390575862</v>
       </c>
       <c r="F45">
-        <v>6.264993050536724</v>
+        <v>5.907661860725907</v>
       </c>
       <c r="G45">
-        <v>-7.907735962745771</v>
+        <v>-5.125936691395038</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.38299271832882</v>
       </c>
       <c r="E46">
-        <v>-15.21819546476564</v>
+        <v>-12.84221387042375</v>
       </c>
       <c r="F46">
-        <v>6.149922877879039</v>
+        <v>6.324787923140404</v>
       </c>
       <c r="G46">
-        <v>-8.592544711973151</v>
+        <v>-5.936105563653904</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.368678661834228</v>
       </c>
       <c r="E47">
-        <v>-14.27949910076187</v>
+        <v>-12.38467949803534</v>
       </c>
       <c r="F47">
-        <v>6.65151425088739</v>
+        <v>6.604042171767756</v>
       </c>
       <c r="G47">
-        <v>-9.082292984447795</v>
+        <v>-5.859307900761716</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.346850248194737</v>
       </c>
       <c r="E48">
-        <v>-12.9076269487898</v>
+        <v>-11.9321082131801</v>
       </c>
       <c r="F48">
-        <v>6.405987809432422</v>
+        <v>6.199853551450182</v>
       </c>
       <c r="G48">
-        <v>-8.871137267290848</v>
+        <v>-5.577417975025441</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.32829281109352</v>
       </c>
       <c r="E49">
-        <v>-14.07219571069438</v>
+        <v>-11.53700491342651</v>
       </c>
       <c r="F49">
-        <v>6.316938313631475</v>
+        <v>6.207807535251863</v>
       </c>
       <c r="G49">
-        <v>-9.135847188245302</v>
+        <v>-5.821707957160502</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.328919275717159</v>
       </c>
       <c r="E50">
-        <v>-13.87208568264149</v>
+        <v>-10.86513161098635</v>
       </c>
       <c r="F50">
-        <v>6.5873074934964</v>
+        <v>6.092672749936759</v>
       </c>
       <c r="G50">
-        <v>-8.632012643329306</v>
+        <v>-6.133423029105655</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.358902946967127</v>
       </c>
       <c r="E51">
-        <v>-14.14230191785748</v>
+        <v>-10.48485942887372</v>
       </c>
       <c r="F51">
-        <v>5.703807269836171</v>
+        <v>6.041994888968292</v>
       </c>
       <c r="G51">
-        <v>-8.651988755568208</v>
+        <v>-6.677285510092601</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.427841130032111</v>
       </c>
       <c r="E52">
-        <v>-12.16247023252304</v>
+        <v>-10.8251777180415</v>
       </c>
       <c r="F52">
-        <v>6.429095946500917</v>
+        <v>6.161157196595806</v>
       </c>
       <c r="G52">
-        <v>-8.955408186575099</v>
+        <v>-6.741212202150601</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.540584564423533</v>
       </c>
       <c r="E53">
-        <v>-10.87823083950486</v>
+        <v>-9.544053233516937</v>
       </c>
       <c r="F53">
-        <v>6.418617098855504</v>
+        <v>5.821806549630155</v>
       </c>
       <c r="G53">
-        <v>-9.130736655708198</v>
+        <v>-7.003910544397603</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.696161400086103</v>
       </c>
       <c r="E54">
-        <v>-11.8345368195259</v>
+        <v>-9.892030044367695</v>
       </c>
       <c r="F54">
-        <v>6.338073279546502</v>
+        <v>6.135602062219442</v>
       </c>
       <c r="G54">
-        <v>-9.16443875763488</v>
+        <v>-7.050076341002259</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.895290990260704</v>
       </c>
       <c r="E55">
-        <v>-10.89164571208405</v>
+        <v>-9.59885485694805</v>
       </c>
       <c r="F55">
-        <v>5.658987623140301</v>
+        <v>6.125065228855831</v>
       </c>
       <c r="G55">
-        <v>-9.456549748445363</v>
+        <v>-7.687736348286427</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.129972766050283</v>
       </c>
       <c r="E56">
-        <v>-9.651060723301145</v>
+        <v>-8.868981958356656</v>
       </c>
       <c r="F56">
-        <v>5.875958583485964</v>
+        <v>5.642243004460112</v>
       </c>
       <c r="G56">
-        <v>-9.076904407611739</v>
+        <v>-7.523127596444439</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.396109224239501</v>
       </c>
       <c r="E57">
-        <v>-10.94594895015619</v>
+        <v>-9.173021946602054</v>
       </c>
       <c r="F57">
-        <v>6.216497109307229</v>
+        <v>6.00753149154222</v>
       </c>
       <c r="G57">
-        <v>-9.699211931327865</v>
+        <v>-7.494722695293127</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.684067745800913</v>
       </c>
       <c r="E58">
-        <v>-11.94352539111205</v>
+        <v>-8.2926075971196</v>
       </c>
       <c r="F58">
-        <v>5.867061917579897</v>
+        <v>5.780921648097583</v>
       </c>
       <c r="G58">
-        <v>-10.37091474270786</v>
+        <v>-7.697723751719732</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.986145343477226</v>
       </c>
       <c r="E59">
-        <v>-10.59827947694346</v>
+        <v>-8.530038382137398</v>
       </c>
       <c r="F59">
-        <v>6.20219948793491</v>
+        <v>5.505688294843419</v>
       </c>
       <c r="G59">
-        <v>-10.75064884885758</v>
+        <v>-8.664975904536702</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.295742259404918</v>
       </c>
       <c r="E60">
-        <v>-8.697803200392523</v>
+        <v>-7.282255878128561</v>
       </c>
       <c r="F60">
-        <v>6.099145612822235</v>
+        <v>5.692541473158098</v>
       </c>
       <c r="G60">
-        <v>-10.31098901673574</v>
+        <v>-7.772619487177294</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.60369632816058</v>
       </c>
       <c r="E61">
-        <v>-11.21766449466045</v>
+        <v>-7.033129650020046</v>
       </c>
       <c r="F61">
-        <v>5.927625515133375</v>
+        <v>6.090744310623043</v>
       </c>
       <c r="G61">
-        <v>-10.5936177831913</v>
+        <v>-8.804016329225622</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.909578524863194</v>
       </c>
       <c r="E62">
-        <v>-10.53670811905288</v>
+        <v>-8.256150708110255</v>
       </c>
       <c r="F62">
-        <v>5.883365844801797</v>
+        <v>5.73739756801969</v>
       </c>
       <c r="G62">
-        <v>-10.36600915362115</v>
+        <v>-8.784545396065099</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.206403148660198</v>
       </c>
       <c r="E63">
-        <v>-9.930040234412527</v>
+        <v>-7.298980860133645</v>
       </c>
       <c r="F63">
-        <v>5.635841381171277</v>
+        <v>5.711267546665783</v>
       </c>
       <c r="G63">
-        <v>-10.97847678097338</v>
+        <v>-8.83949373747426</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.495589967117152</v>
       </c>
       <c r="E64">
-        <v>-9.623217594579494</v>
+        <v>-7.019760462765423</v>
       </c>
       <c r="F64">
-        <v>6.061706719685309</v>
+        <v>5.950488455450642</v>
       </c>
       <c r="G64">
-        <v>-10.71627709094328</v>
+        <v>-9.297355680885344</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.775444595810344</v>
       </c>
       <c r="E65">
-        <v>-11.4489485269175</v>
+        <v>-7.105275083943642</v>
       </c>
       <c r="F65">
-        <v>5.50491625642401</v>
+        <v>5.770959701711516</v>
       </c>
       <c r="G65">
-        <v>-10.6334825477253</v>
+        <v>-9.20971037421708</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.046243520253213</v>
       </c>
       <c r="E66">
-        <v>-11.457329707371</v>
+        <v>-7.737971143956697</v>
       </c>
       <c r="F66">
-        <v>5.511791705867245</v>
+        <v>5.521589635507558</v>
       </c>
       <c r="G66">
-        <v>-10.36598435154754</v>
+        <v>-9.520798867460366</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.311548038526491</v>
       </c>
       <c r="E67">
-        <v>-9.760713808699267</v>
+        <v>-7.769693372055738</v>
       </c>
       <c r="F67">
-        <v>5.666083418312682</v>
+        <v>5.623329719919393</v>
       </c>
       <c r="G67">
-        <v>-11.52885045897056</v>
+        <v>-9.274005181262426</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.570014707028102</v>
       </c>
       <c r="E68">
-        <v>-8.873185008217382</v>
+        <v>-7.37722320828209</v>
       </c>
       <c r="F68">
-        <v>5.910483280099842</v>
+        <v>5.859301771750472</v>
       </c>
       <c r="G68">
-        <v>-10.98233807222363</v>
+        <v>-8.772554246158116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.829374599107323</v>
       </c>
       <c r="E69">
-        <v>-9.276657028790501</v>
+        <v>-7.644033810211726</v>
       </c>
       <c r="F69">
-        <v>5.926089721968585</v>
+        <v>5.509796997161304</v>
       </c>
       <c r="G69">
-        <v>-11.41083827659076</v>
+        <v>-9.144142829183565</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.088326863321173</v>
       </c>
       <c r="E70">
-        <v>-9.692505619111607</v>
+        <v>-6.855725228279995</v>
       </c>
       <c r="F70">
-        <v>5.88145231610133</v>
+        <v>5.970601215990613</v>
       </c>
       <c r="G70">
-        <v>-12.02868403780067</v>
+        <v>-8.70803883119482</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.353427546695867</v>
       </c>
       <c r="E71">
-        <v>-9.78218591124863</v>
+        <v>-7.771952719016444</v>
       </c>
       <c r="F71">
-        <v>5.678109656266525</v>
+        <v>5.673903206595109</v>
       </c>
       <c r="G71">
-        <v>-10.42615026602204</v>
+        <v>-9.033342828736718</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.625829717968626</v>
       </c>
       <c r="E72">
-        <v>-9.50945282996979</v>
+        <v>-6.707617559225284</v>
       </c>
       <c r="F72">
-        <v>6.453047361585462</v>
+        <v>5.961333441488092</v>
       </c>
       <c r="G72">
-        <v>-10.2112037477188</v>
+        <v>-9.455201298864052</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.90767179165141</v>
       </c>
       <c r="E73">
-        <v>-7.323966579463814</v>
+        <v>-8.12985155172222</v>
       </c>
       <c r="F73">
-        <v>5.544338261123238</v>
+        <v>5.652095606349009</v>
       </c>
       <c r="G73">
-        <v>-10.43388329150092</v>
+        <v>-8.998422814458282</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.20213356578352</v>
       </c>
       <c r="E74">
-        <v>-9.646388360560712</v>
+        <v>-7.412944978886941</v>
       </c>
       <c r="F74">
-        <v>5.517649920139844</v>
+        <v>5.817018586041974</v>
       </c>
       <c r="G74">
-        <v>-11.01025345876411</v>
+        <v>-8.898997828194915</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.5054282377241</v>
       </c>
       <c r="E75">
-        <v>-10.89993136867709</v>
+        <v>-7.14155338486602</v>
       </c>
       <c r="F75">
-        <v>5.475499273215793</v>
+        <v>5.80660766452359</v>
       </c>
       <c r="G75">
-        <v>-11.54955888506727</v>
+        <v>-9.203838809631666</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.81886195771443</v>
       </c>
       <c r="E76">
-        <v>-9.039425597916294</v>
+        <v>-7.750887631176914</v>
       </c>
       <c r="F76">
-        <v>6.373196057425201</v>
+        <v>5.759846324635557</v>
       </c>
       <c r="G76">
-        <v>-12.38855037761203</v>
+        <v>-9.145564379613427</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.1313153926314</v>
       </c>
       <c r="E77">
-        <v>-10.00388017855665</v>
+        <v>-8.714171006223673</v>
       </c>
       <c r="F77">
-        <v>5.676769357808795</v>
+        <v>5.672486698336321</v>
       </c>
       <c r="G77">
-        <v>-11.03326717233477</v>
+        <v>-8.295545101915808</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.43765186801439</v>
       </c>
       <c r="E78">
-        <v>-11.94107499643041</v>
+        <v>-8.291739575952711</v>
       </c>
       <c r="F78">
-        <v>5.884979504502451</v>
+        <v>5.637882478451775</v>
       </c>
       <c r="G78">
-        <v>-10.8490308426568</v>
+        <v>-8.175134950629072</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.72377750679517</v>
       </c>
       <c r="E79">
-        <v>-10.94860285219275</v>
+        <v>-9.057068439624166</v>
       </c>
       <c r="F79">
-        <v>5.756607408090612</v>
+        <v>5.762240306429648</v>
       </c>
       <c r="G79">
-        <v>-11.05619081521704</v>
+        <v>-8.793079920133449</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.97602484486024</v>
       </c>
       <c r="E80">
-        <v>-12.65963870058429</v>
+        <v>-9.764945931039268</v>
       </c>
       <c r="F80">
-        <v>6.100490881484381</v>
+        <v>5.772734064688312</v>
       </c>
       <c r="G80">
-        <v>-10.15059400666381</v>
+        <v>-8.384126360519986</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.17862693991686</v>
       </c>
       <c r="E81">
-        <v>-11.43358579822696</v>
+        <v>-10.52289038497518</v>
       </c>
       <c r="F81">
-        <v>5.274712955186027</v>
+        <v>5.956870197921809</v>
       </c>
       <c r="G81">
-        <v>-10.27242962449729</v>
+        <v>-8.364186798705358</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.3116589520145</v>
       </c>
       <c r="E82">
-        <v>-13.6229137692084</v>
+        <v>-10.73273969358479</v>
       </c>
       <c r="F82">
-        <v>5.902368593022018</v>
+        <v>5.996794193267133</v>
       </c>
       <c r="G82">
-        <v>-9.479418565691221</v>
+        <v>-8.443223175084427</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.35999615312009</v>
       </c>
       <c r="E83">
-        <v>-14.74800210425915</v>
+        <v>-11.62562198346438</v>
       </c>
       <c r="F83">
-        <v>5.680651087458314</v>
+        <v>5.464886230051127</v>
       </c>
       <c r="G83">
-        <v>-10.38132247602033</v>
+        <v>-8.411869437917451</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.30419904860506</v>
       </c>
       <c r="E84">
-        <v>-15.70172894004748</v>
+        <v>-12.70725526842345</v>
       </c>
       <c r="F84">
-        <v>5.907405066831039</v>
+        <v>5.748494377747593</v>
       </c>
       <c r="G84">
-        <v>-10.31571054832876</v>
+        <v>-8.001305048891272</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.13712026377886</v>
       </c>
       <c r="E85">
-        <v>-15.44034243210807</v>
+        <v>-13.35005193837849</v>
       </c>
       <c r="F85">
-        <v>6.097172441668767</v>
+        <v>5.910662207458847</v>
       </c>
       <c r="G85">
-        <v>-10.0793833371966</v>
+        <v>-8.36833135574375</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.84789700401247</v>
       </c>
       <c r="E86">
-        <v>-17.84285058718163</v>
+        <v>-14.09844815947862</v>
       </c>
       <c r="F86">
-        <v>5.015892873650933</v>
+        <v>5.625051067382411</v>
       </c>
       <c r="G86">
-        <v>-10.06268762553643</v>
+        <v>-8.351702218070654</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.44010019634454</v>
       </c>
       <c r="E87">
-        <v>-19.13297923385842</v>
+        <v>-15.98304670913474</v>
       </c>
       <c r="F87">
-        <v>5.655604570667268</v>
+        <v>5.704168438023792</v>
       </c>
       <c r="G87">
-        <v>-9.533305639424094</v>
+        <v>-7.666317799660934</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.91766136122657</v>
       </c>
       <c r="E88">
-        <v>-19.84488534025861</v>
+        <v>-17.19506591042548</v>
       </c>
       <c r="F88">
-        <v>5.411769655448817</v>
+        <v>6.016078586404306</v>
       </c>
       <c r="G88">
-        <v>-9.571710997731666</v>
+        <v>-7.761867135578794</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.29569228945084</v>
       </c>
       <c r="E89">
-        <v>-21.75358082202139</v>
+        <v>-18.81935363387532</v>
       </c>
       <c r="F89">
-        <v>5.563549757928964</v>
+        <v>5.552292244924919</v>
       </c>
       <c r="G89">
-        <v>-9.022325486562218</v>
+        <v>-7.531166079040477</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.59454696656068</v>
       </c>
       <c r="E90">
-        <v>-22.33691181222753</v>
+        <v>-20.42329477504483</v>
       </c>
       <c r="F90">
-        <v>6.144931135909769</v>
+        <v>5.803703408409374</v>
       </c>
       <c r="G90">
-        <v>-8.232149696382098</v>
+        <v>-7.606070952104108</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.833591866137102</v>
       </c>
       <c r="E91">
-        <v>-25.15792245965877</v>
+        <v>-22.00858799736586</v>
       </c>
       <c r="F91">
-        <v>5.491105715084537</v>
+        <v>5.915158585721242</v>
       </c>
       <c r="G91">
-        <v>-8.90917842672796</v>
+        <v>-6.636127121613701</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.041298273729307</v>
       </c>
       <c r="E92">
-        <v>-25.28898534943638</v>
+        <v>-24.01858445655253</v>
       </c>
       <c r="F92">
-        <v>5.183445091480383</v>
+        <v>5.62908687336885</v>
       </c>
       <c r="G92">
-        <v>-9.323220327549503</v>
+        <v>-6.760309798834595</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.232715609470101</v>
       </c>
       <c r="E93">
-        <v>-29.39686644926008</v>
+        <v>-25.7469890347045</v>
       </c>
       <c r="F93">
-        <v>5.423993044844526</v>
+        <v>5.594547266141721</v>
       </c>
       <c r="G93">
-        <v>-7.778079859489607</v>
+        <v>-6.583927894258982</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.433843124690697</v>
       </c>
       <c r="E94">
-        <v>-30.12663967077968</v>
+        <v>-27.52894511967881</v>
       </c>
       <c r="F94">
-        <v>5.046351943051871</v>
+        <v>5.540854147827063</v>
       </c>
       <c r="G94">
-        <v>-8.853177955248581</v>
+        <v>-5.948235083024216</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.654541502669182</v>
       </c>
       <c r="E95">
-        <v>-34.13340461108344</v>
+        <v>-29.84779098582503</v>
       </c>
       <c r="F95">
-        <v>5.348179203405509</v>
+        <v>5.507089892488955</v>
       </c>
       <c r="G95">
-        <v>-7.781892851964928</v>
+        <v>-6.539652276738291</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.904120771960141</v>
       </c>
       <c r="E96">
-        <v>-34.91548129942227</v>
+        <v>-32.90402290984926</v>
       </c>
       <c r="F96">
-        <v>4.397677310737245</v>
+        <v>5.488415177760244</v>
       </c>
       <c r="G96">
-        <v>-7.987928898978702</v>
+        <v>-6.711807385820893</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.189555945394773</v>
       </c>
       <c r="E97">
-        <v>-38.89225590074945</v>
+        <v>-35.12861579818982</v>
       </c>
       <c r="F97">
-        <v>5.005712238270527</v>
+        <v>4.765043343265575</v>
       </c>
       <c r="G97">
-        <v>-8.098654493204704</v>
+        <v>-6.326414490769931</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.500074402823031</v>
       </c>
       <c r="E98">
-        <v>-39.82790380764079</v>
+        <v>-37.81870061181716</v>
       </c>
       <c r="F98">
-        <v>4.687022731065501</v>
+        <v>4.788983161206481</v>
       </c>
       <c r="G98">
-        <v>-6.632686160242613</v>
+        <v>-6.298704047679855</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.848164261334131</v>
       </c>
       <c r="E99">
-        <v>-43.38834389292186</v>
+        <v>-39.54685184407832</v>
       </c>
       <c r="F99">
-        <v>4.468279064477847</v>
+        <v>4.610557792847884</v>
       </c>
       <c r="G99">
-        <v>-8.358761671445025</v>
+        <v>-6.179967383676023</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.207609311798665</v>
       </c>
       <c r="E100">
-        <v>-44.8353019524355</v>
+        <v>-43.82226518232296</v>
       </c>
       <c r="F100">
-        <v>4.682334171565656</v>
+        <v>4.373750746674784</v>
       </c>
       <c r="G100">
-        <v>-7.701180377558366</v>
+        <v>-6.26058456590501</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.612611687723465</v>
       </c>
       <c r="E101">
-        <v>-46.92581568127379</v>
+        <v>-45.21698622639857</v>
       </c>
       <c r="F101">
-        <v>3.859820012834331</v>
+        <v>4.008472200001508</v>
       </c>
       <c r="G101">
-        <v>-7.760518685997484</v>
+        <v>-5.751160416819439</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.019635716025209</v>
       </c>
       <c r="E102">
-        <v>-50.12364407729822</v>
+        <v>-47.7720158758623</v>
       </c>
       <c r="F102">
-        <v>3.830533911675758</v>
+        <v>3.664780907845188</v>
       </c>
       <c r="G102">
-        <v>-8.847519166347343</v>
+        <v>-5.330141301078146</v>
       </c>
     </row>
   </sheetData>
